--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3636363636363636</v>
+        <v>0.3777777777777778</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4366197183098591</v>
+        <v>0.3873239436619718</v>
       </c>
       <c r="D2">
-        <v>0.6451612903225806</v>
+        <v>0.6304347826086957</v>
       </c>
       <c r="E2">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3777777777777778</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.3873239436619718</v>
+        <v>0.4154929577464789</v>
       </c>
       <c r="D2">
-        <v>0.6304347826086957</v>
+        <v>0.5971223021582733</v>
       </c>
       <c r="E2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
